--- a/data/trans_camb/P8_1_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P8_1_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 11,96</t>
+          <t>4,3; 12,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 13,22</t>
+          <t>4,95; 13,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 14,44</t>
+          <t>5,14; 14,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 10,99</t>
+          <t>3,0; 10,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,38</t>
+          <t>1,37; 10,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 16,13</t>
+          <t>7,8; 15,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,32</t>
+          <t>4,86; 10,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,6</t>
+          <t>4,13; 10,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 14,43</t>
+          <t>8,44; 14,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 54,29</t>
+          <t>17,18; 56,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,12; 59,8</t>
+          <t>19,32; 64,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,82; 64,37</t>
+          <t>19,0; 65,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 27,61</t>
+          <t>6,91; 27,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 25,8</t>
+          <t>3,29; 26,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,35; 40,74</t>
+          <t>17,97; 39,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 32,33</t>
+          <t>13,65; 33,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 32,69</t>
+          <t>11,73; 32,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 44,87</t>
+          <t>23,85; 44,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,2</t>
+          <t>0,63; 4,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,84</t>
+          <t>1,65; 4,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 40,81</t>
+          <t>6,46; 43,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,69</t>
+          <t>1,46; 5,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,89</t>
+          <t>3,59; 7,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,85</t>
+          <t>1,14; 7,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,27</t>
+          <t>1,56; 4,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,79</t>
+          <t>3,22; 5,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 24,17</t>
+          <t>5,31; 26,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 82,08</t>
+          <t>9,7; 85,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 100,43</t>
+          <t>26,16; 105,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106,01; 880,33</t>
+          <t>110,74; 960,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 75,32</t>
+          <t>15,36; 73,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,01; 104,05</t>
+          <t>35,66; 101,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 87,86</t>
+          <t>15,89; 94,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,06; 66,76</t>
+          <t>20,36; 65,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,0; 90,03</t>
+          <t>41,86; 92,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75,31; 362,5</t>
+          <t>72,99; 386,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,78</t>
+          <t>-0,69; 6,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,16</t>
+          <t>-0,84; 5,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,05</t>
+          <t>-1,44; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,46</t>
+          <t>-4,1; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,16</t>
+          <t>-4,5; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,32</t>
+          <t>-3,74; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,87</t>
+          <t>-1,26; 3,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,52</t>
+          <t>-1,64; 3,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,42</t>
+          <t>-1,56; 2,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 168,85</t>
+          <t>-14,16; 165,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 141,97</t>
+          <t>-15,87; 147,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 118,06</t>
+          <t>-23,69; 116,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 48,24</t>
+          <t>-37,74; 48,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 44,57</t>
+          <t>-40,94; 43,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 37,04</t>
+          <t>-32,79; 35,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 69,29</t>
+          <t>-16,58; 64,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 61,6</t>
+          <t>-20,33; 54,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 41,65</t>
+          <t>-18,18; 42,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,09</t>
+          <t>1,97; 5,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,33</t>
+          <t>1,22; 4,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 27,5</t>
+          <t>3,03; 27,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,88</t>
+          <t>1,81; 6,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,19</t>
+          <t>-0,88; 3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,61</t>
+          <t>-4,34; 1,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,9</t>
+          <t>2,41; 4,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,36</t>
+          <t>0,76; 3,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 14,46</t>
+          <t>0,94; 14,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,18; 48,17</t>
+          <t>16,67; 49,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 41,43</t>
+          <t>10,38; 41,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,72; 264,05</t>
+          <t>27,05; 254,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,02; 29,24</t>
+          <t>8,18; 30,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 15,49</t>
+          <t>-3,82; 16,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 7,96</t>
+          <t>-20,24; 7,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,81; 31,1</t>
+          <t>14,19; 31,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 21,08</t>
+          <t>4,43; 20,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 90,77</t>
+          <t>5,9; 94,86</t>
         </is>
       </c>
     </row>
